--- a/Burse/Licenta/Etapa_1.xlsx
+++ b/Burse/Licenta/Etapa_1.xlsx
@@ -693,11 +693,11 @@
         <f>(1671770.95/1200)*B30</f>
       </c>
       <c r="D30" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10">
@@ -925,11 +925,11 @@
         <f>(1671770.95/1200)*B38</f>
       </c>
       <c r="D38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="10">
@@ -1552,11 +1552,11 @@
         <f>(1671770.95/1200)*B59</f>
       </c>
       <c r="D59" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="10"/>
       <c r="H59" s="10">
